--- a/artfynd/A 30470-2024 artfynd.xlsx
+++ b/artfynd/A 30470-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,6 +794,215 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>120348694</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Höksberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>552769</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7016937</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120348674</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Höksberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>552948</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7016998</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30470-2024 artfynd.xlsx
+++ b/artfynd/A 30470-2024 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120348694</v>
+        <v>120348674</v>
       </c>
       <c r="B3" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552769</v>
+        <v>552948</v>
       </c>
       <c r="R3" t="n">
-        <v>7016937</v>
+        <v>7016998</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,6 +872,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120348674</v>
+        <v>120348694</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,21 +919,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -938,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552948</v>
+        <v>552769</v>
       </c>
       <c r="R4" t="n">
-        <v>7016998</v>
+        <v>7016937</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,11 +979,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 30470-2024 artfynd.xlsx
+++ b/artfynd/A 30470-2024 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120348674</v>
+        <v>120348694</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552948</v>
+        <v>552769</v>
       </c>
       <c r="R3" t="n">
-        <v>7016998</v>
+        <v>7016937</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,11 +872,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120348694</v>
+        <v>120348674</v>
       </c>
       <c r="B4" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,21 +914,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552769</v>
+        <v>552948</v>
       </c>
       <c r="R4" t="n">
-        <v>7016937</v>
+        <v>7016998</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,6 +974,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 30470-2024 artfynd.xlsx
+++ b/artfynd/A 30470-2024 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102634963</v>
+        <v>120348694</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Höksberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552864.8087472202</v>
+        <v>552769</v>
       </c>
       <c r="R2" t="n">
-        <v>7016984.028727729</v>
+        <v>7016937</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,38 +754,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120348694</v>
+        <v>120348674</v>
       </c>
       <c r="B3" t="n">
-        <v>79645</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552769</v>
+        <v>552948</v>
       </c>
       <c r="R3" t="n">
-        <v>7016937</v>
+        <v>7016998</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,50 +874,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120348674</v>
+        <v>102634939</v>
       </c>
       <c r="B4" t="n">
-        <v>57335</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Höksberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552948</v>
+        <v>552865</v>
       </c>
       <c r="R4" t="n">
-        <v>7016998</v>
+        <v>7016984</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,17 +943,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,21 +957,26 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30470-2024 artfynd.xlsx
+++ b/artfynd/A 30470-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348694</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348674</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,8 +992,18 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102634939</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>